--- a/data/trans_camb/IP41-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 10,43</t>
+          <t>-3,48; 9,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 4,02</t>
+          <t>-12,4; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-94,05; -84,33</t>
+          <t>-94,08; -84,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 6,27</t>
+          <t>-4,88; 6,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 0,63</t>
+          <t>-12,49; 1,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-97,21; -89,29</t>
+          <t>-96,6; -88,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,74</t>
+          <t>-1,9; 6,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 0,45</t>
+          <t>-9,85; 0,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -88,11</t>
+          <t>-94,3; -87,78</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 12,28</t>
+          <t>-3,78; 11,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 4,61</t>
+          <t>-13,37; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 6,91</t>
+          <t>-5,07; 6,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 0,67</t>
+          <t>-12,97; 1,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,54</t>
+          <t>-2,02; 7,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 0,48</t>
+          <t>-10,56; 0,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 3,2</t>
+          <t>-9,71; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,35; -3,72</t>
+          <t>-17,47; -2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-96,49; -86,82</t>
+          <t>-96,16; -86,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 0,28</t>
+          <t>-12,74; 0,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -1,25</t>
+          <t>-13,25; -0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-97,97; -90,66</t>
+          <t>-97,82; -90,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 0,04</t>
+          <t>-9,99; -0,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -3,82</t>
+          <t>-13,52; -3,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-96,38; -89,87</t>
+          <t>-96,43; -90,26</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 3,51</t>
+          <t>-10,17; 3,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -4,16</t>
+          <t>-18,7; -2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 0,31</t>
+          <t>-13,3; -0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -1,47</t>
+          <t>-13,76; -0,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 0,01</t>
+          <t>-10,46; -0,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -4,16</t>
+          <t>-14,29; -3,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 2,73</t>
+          <t>-8,91; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 1,93</t>
+          <t>-11,59; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-98,94; -90,29</t>
+          <t>-98,94; -90,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,23</t>
+          <t>-4,5; 8,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 7,35</t>
+          <t>-6,35; 7,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,59; -85,92</t>
+          <t>-95,08; -85,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,19</t>
+          <t>-4,18; 5,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,06</t>
+          <t>-6,54; 3,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-96,32; -89,81</t>
+          <t>-96,06; -89,58</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 2,98</t>
+          <t>-9,09; 3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 2,0</t>
+          <t>-11,84; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 9,38</t>
+          <t>-4,83; 9,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 8,27</t>
+          <t>-6,78; 8,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,56</t>
+          <t>-4,39; 5,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,53</t>
+          <t>-6,89; 3,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,15</t>
+          <t>-6,96; 2,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -3,68</t>
+          <t>-14,18; -3,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-93,78; -86,74</t>
+          <t>-93,41; -86,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,35</t>
+          <t>-8,7; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -1,59</t>
+          <t>-12,49; -1,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-92,85; -86,06</t>
+          <t>-93,0; -85,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,53</t>
+          <t>-6,56; 0,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -4,19</t>
+          <t>-11,91; -4,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-92,65; -87,92</t>
+          <t>-92,46; -87,7</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 3,53</t>
+          <t>-7,51; 3,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -4,18</t>
+          <t>-15,38; -3,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,71</t>
+          <t>-9,59; 1,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -1,66</t>
+          <t>-13,5; -1,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,59</t>
+          <t>-7,16; 0,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -4,74</t>
+          <t>-13,06; -4,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 2,96</t>
+          <t>-11,93; 2,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 2,28</t>
+          <t>-11,77; 3,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,22; -82,12</t>
+          <t>-92,57; -82,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,33; -3,59</t>
+          <t>-16,35; -4,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -5,67</t>
+          <t>-19,17; -5,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-96,78; -89,27</t>
+          <t>-96,23; -88,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -3,45</t>
+          <t>-12,23; -2,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -3,82</t>
+          <t>-13,62; -3,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-93,85; -87,96</t>
+          <t>-93,72; -87,48</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 3,59</t>
+          <t>-13,05; 2,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 2,6</t>
+          <t>-13,14; 3,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -3,93</t>
+          <t>-17,36; -4,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,7; -6,27</t>
+          <t>-20,25; -6,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -3,9</t>
+          <t>-13,19; -3,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -4,3</t>
+          <t>-14,71; -4,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 7,78</t>
+          <t>-9,75; 7,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 2,6</t>
+          <t>-16,71; 2,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-94,83; -82,29</t>
+          <t>-94,44; -83,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 3,48</t>
+          <t>-14,29; 3,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-32,49; -10,2</t>
+          <t>-32,59; -10,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-94,52; -83,15</t>
+          <t>-94,5; -82,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 3,09</t>
+          <t>-9,9; 3,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -7,29</t>
+          <t>-21,56; -6,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-93,23; -85,29</t>
+          <t>-93,37; -85,16</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 8,96</t>
+          <t>-10,45; 8,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 2,89</t>
+          <t>-18,34; 3,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 4,05</t>
+          <t>-15,28; 3,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,33; -11,82</t>
+          <t>-35,86; -11,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 3,58</t>
+          <t>-10,75; 3,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,93; -8,51</t>
+          <t>-23,62; -7,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,6</t>
+          <t>-4,61; 0,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -4,17</t>
+          <t>-10,08; -4,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-92,46; -88,85</t>
+          <t>-92,49; -88,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,44</t>
+          <t>-6,7; -1,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -4,79</t>
+          <t>-10,78; -4,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-93,46; -90,16</t>
+          <t>-93,51; -90,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -0,95</t>
+          <t>-4,91; -1,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -5,67</t>
+          <t>-9,76; -5,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-92,58; -90,04</t>
+          <t>-92,69; -90,16</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,67</t>
+          <t>-5,03; 0,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -4,71</t>
+          <t>-11,0; -4,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -1,56</t>
+          <t>-7,25; -1,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -5,29</t>
+          <t>-11,6; -5,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,09</t>
+          <t>-5,35; -1,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -6,27</t>
+          <t>-10,57; -6,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">

--- a/data/trans_camb/IP41-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Clase-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-89,73</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>-5,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-5,44</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-93,66</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-4,69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-91,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,96</t>
+          <t>-2,69; 10,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 3,63</t>
+          <t>-12,86; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-94,08; -84,27</t>
+          <t>-5,06; 6,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,08</t>
+          <t>-12,49; 1,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 1,03</t>
+          <t>-2,11; 6,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-96,6; -88,76</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 6,77</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-9,85; 0,47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-94,3; -87,78</t>
+          <t>-9,98; 0,63</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>-5,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-5,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-5,12%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 11,73</t>
+          <t>-2,88; 12,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 4,12</t>
+          <t>-14,04; 3,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,24; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,7</t>
+          <t>-13,2; 1,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 1,08</t>
+          <t>-2,2; 7,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 7,6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-10,56; 0,5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,78; 0,69</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-92,77</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,17</t>
+          <t>-7,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-95,02</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-4,73</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>-8,84</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-93,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 3,6</t>
+          <t>-9,97; 3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; -2,01</t>
+          <t>-18,38; -3,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-96,16; -86,82</t>
+          <t>-12,46; 0,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 0,04</t>
+          <t>-13,32; -1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -0,79</t>
+          <t>-10,06; -0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-97,82; -90,35</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-9,99; -0,25</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-13,52; -3,61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-96,43; -90,26</t>
+          <t>-14,14; -4,21</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-6,49%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,49%</t>
+          <t>-7,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-7,58%</t>
+          <t>-5,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-5,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>-9,42%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 3,96</t>
+          <t>-10,4; 3,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -2,4</t>
+          <t>-19,36; -3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,9; 0,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -0,25</t>
+          <t>-13,81; -1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -0,97</t>
+          <t>-10,42; -0,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,46; -0,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-14,29; -3,9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,84; -4,57</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-96,39</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-91,38</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-1,38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-93,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 3,57</t>
+          <t>-8,52; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 2,44</t>
+          <t>-11,59; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-98,94; -90,03</t>
+          <t>-4,24; 8,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 8,19</t>
+          <t>-6,77; 7,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 7,26</t>
+          <t>-4,76; 4,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,08; -85,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,18; 5,15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-6,54; 3,34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-96,06; -89,58</t>
+          <t>-6,51; 3,19</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-1,48%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 3,8</t>
+          <t>-8,73; 2,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 2,57</t>
+          <t>-11,89; 2,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,48; 10,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 9,28</t>
+          <t>-7,21; 8,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 8,14</t>
+          <t>-4,93; 4,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-4,39; 5,66</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-6,89; 3,65</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,92; 3,5</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-90,55</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,68</t>
+          <t>-6,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-6,98</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-89,99</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-2,91</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-7,89</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-90,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,9</t>
+          <t>-7,35; 2,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -3,28</t>
+          <t>-14,16; -3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-93,41; -86,88</t>
+          <t>-9,2; 1,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,94</t>
+          <t>-12,22; -1,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -1,27</t>
+          <t>-6,94; 0,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-93,0; -85,9</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-6,56; 0,56</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-11,91; -4,26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-92,46; -87,7</t>
+          <t>-11,29; -3,71</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>-7,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-7,76%</t>
+          <t>-3,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-3,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-8,74%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,29</t>
+          <t>-8,0; 3,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -3,76</t>
+          <t>-15,49; -3,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,85; 1,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 1,04</t>
+          <t>-13,25; -2,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -1,37</t>
+          <t>-7,55; 0,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 0,61</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-13,06; -4,82</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-12,38; -4,2</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-87,92</t>
+          <t>-9,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-9,98</t>
+          <t>-12,03</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-12,03</t>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-93,54</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-7,75</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>-8,87</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-91,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 2,5</t>
+          <t>-11,58; 2,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 3,3</t>
+          <t>-12,61; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,57; -82,2</t>
+          <t>-16,19; -3,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -4,09</t>
+          <t>-19,26; -5,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -5,59</t>
+          <t>-12,08; -2,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-96,23; -88,92</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-12,23; -2,92</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-13,62; -3,74</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-93,72; -87,48</t>
+          <t>-13,87; -4,17</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-10,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-10,66%</t>
+          <t>-12,86%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-12,86%</t>
+          <t>-8,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-8,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>-9,75%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 2,94</t>
+          <t>-12,63; 2,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 3,68</t>
+          <t>-13,96; 2,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,34; -3,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -4,51</t>
+          <t>-20,35; -6,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,25; -6,12</t>
+          <t>-13,2; -3,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-13,19; -3,29</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-14,71; -4,18</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-15,01; -4,7</t>
         </is>
       </c>
     </row>
@@ -1714,37 +1383,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-89,87</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-4,81</t>
+          <t>-20,89</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-20,89</t>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-89,65</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
           <t>-13,95</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>-89,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 7,19</t>
+          <t>-10,58; 7,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 2,99</t>
+          <t>-15,97; 2,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -83,42</t>
+          <t>-13,29; 3,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 3,4</t>
+          <t>-31,7; -10,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-32,59; -10,26</t>
+          <t>-9,68; 3,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-94,5; -82,81</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-9,9; 3,19</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-21,56; -6,81</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-93,37; -85,16</t>
+          <t>-21,74; -7,12</t>
         </is>
       </c>
     </row>
@@ -1820,37 +1459,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-5,37%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-5,37%</t>
+          <t>-23,31%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-23,31%</t>
+          <t>-3,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-3,52%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
           <t>-15,54%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 8,53</t>
+          <t>-11,46; 8,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 3,2</t>
+          <t>-17,17; 2,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,42; 4,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 3,88</t>
+          <t>-34,38; -11,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,86; -11,94</t>
+          <t>-10,39; 3,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-10,75; 3,74</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; -7,76</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-23,87; -8,24</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1539,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-90,84</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-8,18</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-8,18</t>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-91,97</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-3,12</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
           <t>-7,72</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-91,43</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,61</t>
+          <t>-4,6; 0,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -4,07</t>
+          <t>-10,08; -4,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-92,49; -88,69</t>
+          <t>-6,73; -1,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,48</t>
+          <t>-10,91; -5,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -4,88</t>
+          <t>-4,83; -1,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-93,51; -90,06</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; -1,18</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-9,76; -5,68</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-92,69; -90,16</t>
+          <t>-9,84; -5,67</t>
         </is>
       </c>
     </row>
@@ -2036,37 +1615,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,47%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-4,47%</t>
+          <t>-8,9%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-8,9%</t>
+          <t>-3,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-3,41%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
           <t>-8,44%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,68</t>
+          <t>-5,0; 0,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -4,58</t>
+          <t>-11,07; -4,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,23; -1,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -1,67</t>
+          <t>-11,75; -5,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -5,38</t>
+          <t>-5,24; -1,33</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; -1,31</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-10,57; -6,28</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,68; -6,3</t>
         </is>
       </c>
     </row>
@@ -2133,11 +1682,11 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/IP41-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>3,75</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-4,32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 10,86</t>
+          <t>-4,41; 6,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 3,04</t>
+          <t>-12,93; 0,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 6,65</t>
+          <t>-2,62; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 1,63</t>
+          <t>-12,08; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 6,44</t>
+          <t>-1,9; 6,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,63</t>
+          <t>-9,81; 0,45</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-5,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-4,82%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 12,79</t>
+          <t>-4,65; 6,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 3,54</t>
+          <t>-13,38; 0,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,44</t>
+          <t>-2,79; 12,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 1,65</t>
+          <t>-13,19; 4,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,25</t>
+          <t>-2,01; 7,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,69</t>
+          <t>-10,49; 0,48</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-6,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-7,2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-3,28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-10,67</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 3,24</t>
+          <t>-13,18; 0,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -3,04</t>
+          <t>-13,46; -1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,22</t>
+          <t>-10,92; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -1,57</t>
+          <t>-18,35; -3,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -0,39</t>
+          <t>-9,28; 0,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -4,21</t>
+          <t>-13,67; -3,82</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-6,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-7,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-3,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-11,5%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 3,58</t>
+          <t>-13,55; 0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -3,43</t>
+          <t>-14,05; -1,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 0,01</t>
+          <t>-11,54; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -1,68</t>
+          <t>-19,58; -4,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -0,41</t>
+          <t>-9,93; 0,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -4,57</t>
+          <t>-14,36; -4,16</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-2,88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-4,29</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 2,67</t>
+          <t>-4,52; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 2,7</t>
+          <t>-6,8; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 8,74</t>
+          <t>-8,55; 2,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 7,49</t>
+          <t>-11,97; 1,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 4,26</t>
+          <t>-4,5; 4,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,19</t>
+          <t>-6,1; 4,06</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-2,99%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-4,45%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 2,82</t>
+          <t>-4,82; 9,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 2,71</t>
+          <t>-7,26; 8,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 10,07</t>
+          <t>-8,69; 2,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 8,35</t>
+          <t>-12,41; 2,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,66</t>
+          <t>-4,71; 4,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 3,5</t>
+          <t>-6,4; 4,53</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,98</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,02</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-8,75</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 2,76</t>
+          <t>-8,06; 2,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -3,43</t>
+          <t>-12,43; -1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,26</t>
+          <t>-7,15; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -1,77</t>
+          <t>-14,67; -3,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,51</t>
+          <t>-6,54; 0,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -3,71</t>
+          <t>-12,24; -4,19</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,09%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-2,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-9,67%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,09%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 3,09</t>
+          <t>-8,87; 2,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -3,97</t>
+          <t>-13,54; -1,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 1,45</t>
+          <t>-7,73; 3,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -2,14</t>
+          <t>-15,77; -4,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,58</t>
+          <t>-7,17; 0,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -4,2</t>
+          <t>-13,45; -4,74</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-9,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-12,03</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-4,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-5,08</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,98</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-12,03</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 2,39</t>
+          <t>-16,33; -3,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 1,79</t>
+          <t>-18,82; -5,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,19; -3,32</t>
+          <t>-11,42; 2,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,26; -5,81</t>
+          <t>-12,46; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -2,86</t>
+          <t>-12,43; -3,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -4,17</t>
+          <t>-13,58; -3,82</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-10,66%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-12,86%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-5,59%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-5,78%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-10,66%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-12,86%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,85</t>
+          <t>-17,01; -3,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 2,05</t>
+          <t>-19,7; -6,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -3,68</t>
+          <t>-12,44; 3,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,35; -6,42</t>
+          <t>-13,64; 2,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -3,26</t>
+          <t>-13,4; -3,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -4,7</t>
+          <t>-14,68; -4,3</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,81</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-20,89</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-6,23</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-20,89</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 7,54</t>
+          <t>-13,7; 3,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 2,85</t>
+          <t>-32,49; -10,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 3,61</t>
+          <t>-10,67; 7,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -10,35</t>
+          <t>-16,86; 2,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 3,32</t>
+          <t>-9,59; 3,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -7,12</t>
+          <t>-21,83; -7,29</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-5,37%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-23,31%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-0,94%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-6,93%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-5,37%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 8,75</t>
+          <t>-14,78; 4,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 2,6</t>
+          <t>-35,33; -11,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 4,15</t>
+          <t>-11,75; 8,96</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -11,7</t>
+          <t>-18,35; 2,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 3,71</t>
+          <t>-10,57; 3,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,87; -8,24</t>
+          <t>-23,93; -8,51</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-4,11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-8,18</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-2,07</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-7,22</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,11</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-8,18</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,53</t>
+          <t>-6,61; -1,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -4,23</t>
+          <t>-10,9; -4,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -1,49</t>
+          <t>-4,75; 0,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,91; -5,21</t>
+          <t>-10,33; -4,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -1,21</t>
+          <t>-4,83; -0,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -5,67</t>
+          <t>-9,72; -5,67</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-4,47%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-8,9%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-2,28%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-7,95%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-4,47%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-8,9%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,53</t>
+          <t>-7,06; -1,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -4,76</t>
+          <t>-11,8; -5,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -1,64</t>
+          <t>-5,17; 0,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -5,68</t>
+          <t>-11,28; -4,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -1,33</t>
+          <t>-5,23; -1,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -6,3</t>
+          <t>-10,57; -6,27</t>
         </is>
       </c>
     </row>
